--- a/basedatos_partidas/salida/descompuestos/CT-06-03-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-03-030.xlsx
@@ -539,10 +539,10 @@
         <v>0.85</v>
       </c>
       <c r="G10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>3.8</v>
       </c>
       <c r="G11" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
-        <v>8.93</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1</v>
+        <v>11.3</v>
       </c>
       <c r="H12" t="n">
-        <v>12.81</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="13">
@@ -669,10 +669,10 @@
         <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="16">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>30.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -906,10 +906,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>34.39</v>
+        <v>43.99</v>
       </c>
       <c r="H28" t="n">
-        <v>0.34</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="29">
@@ -925,7 +925,7 @@
       </c>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>34.73</v>
+        <v>44.43</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-03-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-03-030.xlsx
@@ -721,10 +721,10 @@
         <v>0.1</v>
       </c>
       <c r="G17" t="n">
-        <v>8.5</v>
+        <v>32</v>
       </c>
       <c r="H17" t="n">
-        <v>0.85</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="18">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>40</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="19">
@@ -906,10 +906,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>43.99</v>
+        <v>46.34</v>
       </c>
       <c r="H28" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="29">
@@ -925,7 +925,7 @@
       </c>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>44.43</v>
+        <v>46.8</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-03-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-03-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 06 Paredes y tabiquería</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Tabiquería de yeso laminado</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
